--- a/BoutiquePath_Money_Tracker.xlsx
+++ b/BoutiquePath_Money_Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\MicroStep\RootPath\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/04e9bb415d956f31/Desktop/solfound/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C1C542-AEEC-4AB8-AD0E-94DFB2D580DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{65C1C542-AEEC-4AB8-AD0E-94DFB2D580DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF3BED86-311A-4A5E-B32F-657B0413A507}"/>
   <bookViews>
-    <workbookView xWindow="20670" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11730" yWindow="-16695" windowWidth="29040" windowHeight="15720" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="132">
   <si>
     <t>💰  MICRO-BUSINESS MONEY TRACKER — Dashboard</t>
   </si>
@@ -432,6 +432,9 @@
   </si>
   <si>
     <t>Seedling Sales</t>
+  </si>
+  <si>
+    <t>Raw Materials</t>
   </si>
 </sst>
 </file>
@@ -5398,18 +5401,18 @@
         <v>5</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="E4" s="28">
         <v>10</v>
       </c>
       <c r="F4" s="38" t="str">
         <f t="shared" ref="F4:F35" si="1">IF(D4="","",IF(D4="Seeds &amp; Soil","Yes",IF(D4="Tools &amp; Equipment","Yes",IF(D4="Bags &amp; Packaging","Yes",IF(D4="Water/Electricity","Partial",IF(D4="Transportation / Gas","Yes",IF(D4="Marketing","Yes",IF(D4="Insurance","Yes",IF(D4="Permits / Filing","Yes",IF(D4="Phone / Internet","Partial","Verify"))))))))))</f>
-        <v>Yes</v>
+        <v>Verify</v>
       </c>
       <c r="G4" s="39"/>
       <c r="H4" s="40" t="str">
-        <f t="shared" ref="H4:H35" si="2">IF(D4="","",IF(D4="Seeds &amp; Soil","Schedule C supplies",IF(D4="Tools &amp; Equipment","Depreciate or Section 179",IF(D4="Bags &amp; Packaging","Schedule C supplies",IF(D4="Water/Electricity","Business portion only — estimate %",IF(D4="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D4="Marketing","Fully deductible",IF(D4="Insurance","Business insurance — fully deductible",IF(D4="Permits / Filing","Business licenses",IF(D4="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
+        <f>IF(D4="","",IF(D4="Raw Materials","Schedule C supplies",IF(D4="Tools &amp; Equipment","Depreciate or Section 179",IF(D4="Bags &amp; Packaging","Schedule C supplies",IF(D4="Water/Electricity","Business portion only — estimate %",IF(D4="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D4="Marketing","Fully deductible",IF(D4="Insurance","Business insurance — fully deductible",IF(D4="Permits / Filing","Business licenses",IF(D4="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
         <v>Schedule C supplies</v>
       </c>
     </row>
@@ -5436,7 +5439,7 @@
       </c>
       <c r="G5" s="33"/>
       <c r="H5" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H4:H35" si="2">IF(D5="","",IF(D5="Seeds &amp; Soil","Schedule C supplies",IF(D5="Tools &amp; Equipment","Depreciate or Section 179",IF(D5="Bags &amp; Packaging","Schedule C supplies",IF(D5="Water/Electricity","Business portion only — estimate %",IF(D5="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D5="Marketing","Fully deductible",IF(D5="Insurance","Business insurance — fully deductible",IF(D5="Permits / Filing","Business licenses",IF(D5="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
         <v>Schedule C supplies</v>
       </c>
     </row>
@@ -9626,9 +9629,12 @@
       <formula>F4="Verify"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="D4:D500" xr:uid="{00000000-0002-0000-0200-000000000000}">
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="D204:D500" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Seeds &amp; Soil,Tools &amp; Equipment,Bags &amp; Packaging,Water/Electricity,Transportation / Gas,Marketing,Insurance,Permits / Filing,Phone / Internet,Other Expense"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="D4:D203" xr:uid="{4FC9D185-2F99-4B65-A937-97F0755E8B60}">
+      <formula1>"Raw Materials,Tools &amp; Equipment,Bags &amp; Packaging,Water/Electricity,Transportation / Gas,Marketing,Insurance,Permits / Filing,Phone / Internet,Other Expense"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9705,11 +9711,11 @@
       </c>
       <c r="B6" s="43">
         <f>IFERROR(SUMIF('Expense Log'!F4:F203,"Yes",'Expense Log'!E4:E203),0)</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C6" s="44">
         <f>IFERROR(B6/B5,0)</f>
-        <v>0.19006709368407049</v>
+        <v>0.16630870697356168</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>51</v>
@@ -9737,11 +9743,11 @@
       </c>
       <c r="B8" s="11">
         <f>B5-B6</f>
-        <v>340.904</v>
+        <v>350.904</v>
       </c>
       <c r="C8" s="44">
         <f>IFERROR(B8/B5,0)</f>
-        <v>0.80993290631592951</v>
+        <v>0.8336912930264383</v>
       </c>
       <c r="D8" s="34" t="s">
         <v>55</v>
@@ -9753,11 +9759,11 @@
       </c>
       <c r="B9" s="5">
         <f>B8*0.153</f>
-        <v>52.158311999999995</v>
+        <v>53.688311999999996</v>
       </c>
       <c r="C9" s="42">
         <f>IFERROR(B9/B5,0)</f>
-        <v>0.12391973466633721</v>
+        <v>0.12755476783304506</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>57</v>
@@ -9769,11 +9775,11 @@
       </c>
       <c r="B10" s="10">
         <f>B8*0.12</f>
-        <v>40.908479999999997</v>
+        <v>42.10848</v>
       </c>
       <c r="C10" s="44">
         <f>IFERROR(B10/B5,0)</f>
-        <v>9.7191948757911539E-2</v>
+        <v>0.1000429551631726</v>
       </c>
       <c r="D10" s="34" t="s">
         <v>59</v>
@@ -9785,11 +9791,11 @@
       </c>
       <c r="B11" s="15">
         <f>B9+B10</f>
-        <v>93.066791999999992</v>
+        <v>95.796791999999996</v>
       </c>
       <c r="C11" s="42">
         <f>IFERROR(B11/B5,0)</f>
-        <v>0.22111168342424875</v>
+        <v>0.22759772299621767</v>
       </c>
       <c r="D11" s="30" t="s">
         <v>61</v>
@@ -9801,11 +9807,11 @@
       </c>
       <c r="B12" s="46">
         <f>B8-B11</f>
-        <v>247.837208</v>
+        <v>255.10720800000001</v>
       </c>
       <c r="C12" s="44">
         <f>IFERROR(B12/B5,0)</f>
-        <v>0.58882122289168082</v>
+        <v>0.60609357003022069</v>
       </c>
       <c r="D12" s="34" t="s">
         <v>63</v>
@@ -9927,7 +9933,7 @@
       </c>
       <c r="B25" s="45">
         <f>IFERROR(SUMIF('Expense Log'!D4:D203,"Seeds &amp; Soil",'Expense Log'!E4:E203),0)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C25" s="52" t="s">
         <v>77</v>
